--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-06-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-06-2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA7F53A-232E-4B13-B1FE-329F6BC841AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBF63C4-6BBD-491E-ADDD-59C8AD6312AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -840,6 +840,24 @@
     <xf numFmtId="10" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -888,19 +906,67 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -915,67 +981,63 @@
     <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -990,73 +1052,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1543,74 +1543,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="85"/>
-      <c r="B1" s="86"/>
-      <c r="C1" s="93" t="s">
+      <c r="A1" s="91"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="90" t="s">
+      <c r="A2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="98"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="85"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="98" t="s">
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="106"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="89"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="95"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65"/>
       <c r="B6" s="65"/>
       <c r="C6" s="65"/>
       <c r="D6" s="66"/>
-      <c r="E6" s="95" t="str">
+      <c r="E6" s="101" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 06 năm 2026</v>
       </c>
-      <c r="F6" s="95"/>
+      <c r="F6" s="101"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1685,7 +1685,7 @@
       <c r="D12" s="81">
         <v>3000</v>
       </c>
-      <c r="E12" s="158">
+      <c r="E12" s="85">
         <f>SUM(C12*D12)</f>
         <v>600000</v>
       </c>
@@ -1694,10 +1694,10 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="101" t="s">
+      <c r="A13" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="102"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="50">
         <f>SUM(C12:C12)</f>
         <v>200</v>
@@ -1707,12 +1707,12 @@
       <c r="F13" s="46"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="103" t="s">
+      <c r="A14" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="49">
         <f>SUM(E11:E12)</f>
         <v>1746000</v>
@@ -1736,33 +1736,33 @@
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="104" t="s">
+      <c r="A17" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="104"/>
+      <c r="B17" s="89"/>
       <c r="C17" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="104" t="s">
+      <c r="D17" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="104"/>
+      <c r="E17" s="89"/>
       <c r="F17" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="105"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="105" t="s">
+      <c r="D18" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="105"/>
+      <c r="E18" s="90"/>
       <c r="F18" s="27" t="s">
         <v>7</v>
       </c>
@@ -1800,17 +1800,17 @@
       <c r="F22" s="22"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="104"/>
+      <c r="B23" s="89"/>
       <c r="C23" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="104"/>
+      <c r="E23" s="89"/>
       <c r="F23" s="9" t="s">
         <v>9</v>
       </c>
@@ -1849,6 +1849,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A17:B17"/>
@@ -1857,14 +1865,6 @@
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C3:F3"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1897,64 +1897,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="117"/>
-      <c r="B1" s="118"/>
-      <c r="C1" s="119" t="s">
+      <c r="A1" s="114"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="117"/>
-      <c r="B2" s="118"/>
-      <c r="C2" s="128" t="s">
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="125" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="130"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="127"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="117"/>
-      <c r="B3" s="118"/>
-      <c r="C3" s="98" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="100"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="106"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="117"/>
-      <c r="B4" s="118"/>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="89"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="95"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="120" t="s">
+      <c r="A5" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="121"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="123"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="120"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="70"/>
@@ -2003,10 +2003,10 @@
       <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="124" t="s">
+      <c r="A10" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="125"/>
+      <c r="B10" s="122"/>
       <c r="C10" s="48">
         <f>'Bảng tính CK'!E14</f>
         <v>1746000</v>
@@ -2018,10 +2018,10 @@
       <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="110" t="s">
+      <c r="A11" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="111"/>
+      <c r="B11" s="108"/>
       <c r="C11" s="48">
         <v>3</v>
       </c>
@@ -2032,10 +2032,10 @@
       <c r="H11" s="28"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="126" t="s">
+      <c r="A12" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="127"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="46">
         <v>1</v>
       </c>
@@ -2046,10 +2046,10 @@
       <c r="H12" s="28"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="116"/>
+      <c r="B13" s="113"/>
       <c r="C13" s="46">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>0</v>
@@ -2181,11 +2181,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="112" t="s">
+      <c r="A19" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="113"/>
-      <c r="C19" s="114"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
       <c r="D19" s="84">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2218,11 +2218,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="101" t="s">
+      <c r="A21" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="106"/>
-      <c r="C21" s="102"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="33"/>
       <c r="E21" s="49">
         <f>SUM(E16:E18)</f>
@@ -2265,40 +2265,40 @@
       <c r="H23" s="57"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="107" t="s">
+      <c r="A24" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="107"/>
-      <c r="C24" s="107" t="s">
+      <c r="B24" s="129"/>
+      <c r="C24" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="107"/>
-      <c r="E24" s="108" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="108"/>
-      <c r="G24" s="107" t="s">
+      <c r="F24" s="130"/>
+      <c r="G24" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="107"/>
+      <c r="H24" s="129"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="105" t="s">
+      <c r="A25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="105" t="s">
+      <c r="B25" s="90"/>
+      <c r="C25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="105"/>
-      <c r="E25" s="109" t="s">
+      <c r="D25" s="90"/>
+      <c r="E25" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="109"/>
-      <c r="G25" s="105" t="s">
+      <c r="F25" s="131"/>
+      <c r="G25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="105"/>
+      <c r="H25" s="90"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
@@ -2341,36 +2341,25 @@
       <c r="H29" s="57"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="107" t="s">
+      <c r="A30" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="107"/>
-      <c r="C30" s="107" t="s">
+      <c r="B30" s="129"/>
+      <c r="C30" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="107"/>
-      <c r="E30" s="108" t="s">
+      <c r="D30" s="129"/>
+      <c r="E30" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="108"/>
-      <c r="G30" s="107" t="s">
+      <c r="F30" s="130"/>
+      <c r="G30" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="107"/>
+      <c r="H30" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A30:B30"/>
@@ -2384,6 +2373,17 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2409,59 +2409,59 @@
     <col min="5" max="5" width="16.42578125" customWidth="1"/>
     <col min="6" max="6" width="24.28515625" customWidth="1"/>
     <col min="7" max="7" width="19.28515625" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="141"/>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="142" t="s">
+      <c r="A1" s="140"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="148" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="149"/>
+      <c r="H1" s="148"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="141"/>
-      <c r="B2" s="141"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="145"/>
-      <c r="G2" s="148" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="149"/>
+      <c r="H2" s="148"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="141"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="148" t="s">
+      <c r="A3" s="140"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="149"/>
+      <c r="H3" s="148"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="140" t="str">
+      <c r="A4" s="139" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 06 năm 2026</v>
       </c>
-      <c r="B4" s="140"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="140"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
@@ -2498,27 +2498,27 @@
       <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="150" t="s">
+      <c r="A8" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="150" t="s">
+      <c r="B8" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="152" t="s">
+      <c r="C8" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="153"/>
-      <c r="E8" s="153"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="155" t="s">
+      <c r="D8" s="136"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="155"/>
+      <c r="H8" s="138"/>
       <c r="I8" s="55"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="151"/>
-      <c r="B9" s="151"/>
+      <c r="A9" s="134"/>
+      <c r="B9" s="134"/>
       <c r="C9" s="37" t="s">
         <v>61</v>
       </c>
@@ -2531,11 +2531,11 @@
       <c r="F9" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="155"/>
-      <c r="H9" s="155"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
       <c r="I9" s="55"/>
     </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="79">
         <v>1</v>
       </c>
@@ -2555,13 +2555,13 @@
         <f>D10-E10</f>
         <v>2</v>
       </c>
-      <c r="G10" s="135" t="s">
+      <c r="G10" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="135"/>
+      <c r="H10" s="132"/>
       <c r="I10" s="55"/>
     </row>
-    <row r="11" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="79">
         <v>2</v>
       </c>
@@ -2581,13 +2581,13 @@
         <f>SUM(D11-E11)</f>
         <v>12</v>
       </c>
-      <c r="G11" s="131" t="s">
+      <c r="G11" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="132"/>
+      <c r="H11" s="154"/>
       <c r="I11" s="55"/>
     </row>
-    <row r="12" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="79">
         <v>3</v>
       </c>
@@ -2607,13 +2607,13 @@
         <f>SUM(D12-E12)</f>
         <v>2800</v>
       </c>
-      <c r="G12" s="131" t="s">
+      <c r="G12" s="153" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="132"/>
+      <c r="H12" s="154"/>
       <c r="I12" s="55"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="79">
         <v>4</v>
       </c>
@@ -2633,13 +2633,13 @@
         <f>D13-E13</f>
         <v>2</v>
       </c>
-      <c r="G13" s="135" t="s">
+      <c r="G13" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="135"/>
+      <c r="H13" s="132"/>
       <c r="I13" s="55"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="79">
         <v>5</v>
       </c>
@@ -2659,13 +2659,13 @@
         <f t="shared" ref="F14" si="0">D14</f>
         <v>178</v>
       </c>
-      <c r="G14" s="135" t="s">
+      <c r="G14" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="135"/>
+      <c r="H14" s="132"/>
       <c r="I14" s="55"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="79">
         <v>6</v>
       </c>
@@ -2685,12 +2685,12 @@
         <f>D15-E15</f>
         <v>52</v>
       </c>
-      <c r="G15" s="135" t="s">
+      <c r="G15" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="135"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H15" s="132"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79">
         <v>7</v>
       </c>
@@ -2710,12 +2710,12 @@
         <f>D16-E16</f>
         <v>22</v>
       </c>
-      <c r="G16" s="135" t="s">
+      <c r="G16" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="135"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H16" s="132"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="79">
         <v>8</v>
       </c>
@@ -2735,12 +2735,12 @@
         <f>D17-E17</f>
         <v>2</v>
       </c>
-      <c r="G17" s="135" t="s">
+      <c r="G17" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="135"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="132"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="79">
         <v>9</v>
       </c>
@@ -2759,12 +2759,12 @@
       <c r="F18" s="41">
         <v>3</v>
       </c>
-      <c r="G18" s="135" t="s">
+      <c r="G18" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="135"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H18" s="132"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="79">
         <v>10</v>
       </c>
@@ -2782,12 +2782,12 @@
         <f>SUM(D19-E19)</f>
         <v>10</v>
       </c>
-      <c r="G19" s="156" t="s">
+      <c r="G19" s="151" t="s">
         <v>76</v>
       </c>
-      <c r="H19" s="157"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H19" s="152"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="79">
         <v>11</v>
       </c>
@@ -2807,16 +2807,16 @@
         <f>SUM(D20-E20)</f>
         <v>59</v>
       </c>
-      <c r="G20" s="135" t="s">
+      <c r="G20" s="132" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="135"/>
+      <c r="H20" s="132"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="136" t="s">
+      <c r="A21" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="137"/>
+      <c r="B21" s="158"/>
       <c r="C21" s="82">
         <f>SUM(C10:C20)</f>
         <v>6460</v>
@@ -2833,8 +2833,8 @@
         <f>SUM(F10:F20)</f>
         <v>3142</v>
       </c>
-      <c r="G21" s="138"/>
-      <c r="H21" s="139"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="150"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
@@ -2847,40 +2847,40 @@
       <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="134" t="s">
+      <c r="A23" s="156" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="134"/>
-      <c r="C23" s="134" t="s">
+      <c r="B23" s="156"/>
+      <c r="C23" s="156" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134" t="s">
+      <c r="D23" s="156"/>
+      <c r="E23" s="156" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="134"/>
-      <c r="G23" s="104" t="s">
+      <c r="F23" s="156"/>
+      <c r="G23" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="104"/>
+      <c r="H23" s="89"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="105" t="s">
+      <c r="A24" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="105"/>
-      <c r="C24" s="105" t="s">
+      <c r="B24" s="90"/>
+      <c r="C24" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="105"/>
-      <c r="E24" s="105" t="s">
+      <c r="D24" s="90"/>
+      <c r="E24" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="105"/>
-      <c r="G24" s="105" t="s">
+      <c r="F24" s="90"/>
+      <c r="G24" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="105"/>
+      <c r="H24" s="90"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="32"/>
@@ -2923,22 +2923,22 @@
       <c r="H28" s="43"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="133" t="s">
+      <c r="A29" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="133"/>
-      <c r="C29" s="133" t="s">
+      <c r="B29" s="155"/>
+      <c r="C29" s="155" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="133"/>
-      <c r="E29" s="133" t="s">
+      <c r="D29" s="155"/>
+      <c r="E29" s="155" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133" t="s">
+      <c r="F29" s="155"/>
+      <c r="G29" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="H29" s="133"/>
+      <c r="H29" s="155"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="35"/>
@@ -2952,25 +2952,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A29:B29"/>
@@ -2987,9 +2968,28 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="87" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-06-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-06-2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBF63C4-6BBD-491E-ADDD-59C8AD6312AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA81712E-AFDC-438B-B95C-7C81A1A0BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,10 +255,10 @@
     <t>Tồn lô 2/2026, TG102LE-4G (Aithings giữ 4 thiết bị kiểm tra, Makipos giữ 2 mạch fix lỗi chưa trả), 6 mạch lỗi</t>
   </si>
   <si>
-    <t>Chưa xử lý</t>
-  </si>
-  <si>
     <t>Đang chờ test</t>
+  </si>
+  <si>
+    <t>Đang xử lý</t>
   </si>
 </sst>
 </file>
@@ -843,21 +843,6 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -906,6 +891,33 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -969,21 +981,65 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1001,62 +1057,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1543,74 +1543,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="91"/>
-      <c r="B1" s="92"/>
-      <c r="C1" s="99" t="s">
+      <c r="A1" s="86"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="91"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="96" t="s">
+      <c r="A2" s="86"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="98"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="93"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="91"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="104" t="s">
+      <c r="A3" s="86"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="106"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="101"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="91"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="93" t="s">
+      <c r="A4" s="86"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="95"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="90"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="97" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65"/>
       <c r="B6" s="65"/>
       <c r="C6" s="65"/>
       <c r="D6" s="66"/>
-      <c r="E6" s="101" t="str">
+      <c r="E6" s="96" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 06 năm 2026</v>
       </c>
-      <c r="F6" s="101"/>
+      <c r="F6" s="96"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="100"/>
-      <c r="E7" s="100"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1694,10 +1694,10 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="87"/>
+      <c r="B13" s="103"/>
       <c r="C13" s="50">
         <f>SUM(C12:C12)</f>
         <v>200</v>
@@ -1707,12 +1707,12 @@
       <c r="F13" s="46"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="88"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="88"/>
+      <c r="B14" s="104"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="104"/>
       <c r="E14" s="49">
         <f>SUM(E11:E12)</f>
         <v>1746000</v>
@@ -1736,33 +1736,33 @@
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="89" t="s">
+      <c r="A17" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="89"/>
+      <c r="B17" s="105"/>
       <c r="C17" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="89" t="s">
+      <c r="D17" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="89"/>
+      <c r="E17" s="105"/>
       <c r="F17" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="90" t="s">
+      <c r="A18" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="90"/>
+      <c r="B18" s="106"/>
       <c r="C18" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="90" t="s">
+      <c r="D18" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="90"/>
+      <c r="E18" s="106"/>
       <c r="F18" s="27" t="s">
         <v>7</v>
       </c>
@@ -1800,17 +1800,17 @@
       <c r="F22" s="22"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="89" t="s">
+      <c r="A23" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="89"/>
+      <c r="B23" s="105"/>
       <c r="C23" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="89" t="s">
+      <c r="D23" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="89"/>
+      <c r="E23" s="105"/>
       <c r="F23" s="9" t="s">
         <v>9</v>
       </c>
@@ -1849,6 +1849,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D23:E23"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C2:F2"/>
@@ -1857,14 +1865,6 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D23:E23"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1897,64 +1897,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="114"/>
-      <c r="B1" s="115"/>
-      <c r="C1" s="116" t="s">
+      <c r="A1" s="118"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="114"/>
-      <c r="B2" s="115"/>
-      <c r="C2" s="125" t="s">
+      <c r="A2" s="118"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="127"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="131"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="114"/>
-      <c r="B3" s="115"/>
-      <c r="C3" s="104" t="s">
+      <c r="A3" s="118"/>
+      <c r="B3" s="119"/>
+      <c r="C3" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="106"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="101"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="114"/>
-      <c r="B4" s="115"/>
-      <c r="C4" s="93" t="s">
+      <c r="A4" s="118"/>
+      <c r="B4" s="119"/>
+      <c r="C4" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="95"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="90"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="120"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="123"/>
+      <c r="H5" s="124"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="70"/>
@@ -2003,10 +2003,10 @@
       <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="121" t="s">
+      <c r="A10" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="122"/>
+      <c r="B10" s="126"/>
       <c r="C10" s="48">
         <f>'Bảng tính CK'!E14</f>
         <v>1746000</v>
@@ -2018,10 +2018,10 @@
       <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="108"/>
+      <c r="B11" s="112"/>
       <c r="C11" s="48">
         <v>3</v>
       </c>
@@ -2032,10 +2032,10 @@
       <c r="H11" s="28"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="123" t="s">
+      <c r="A12" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="124"/>
+      <c r="B12" s="128"/>
       <c r="C12" s="46">
         <v>1</v>
       </c>
@@ -2046,10 +2046,10 @@
       <c r="H12" s="28"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="112" t="s">
+      <c r="A13" s="116" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="113"/>
+      <c r="B13" s="117"/>
       <c r="C13" s="46">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>0</v>
@@ -2181,11 +2181,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="109" t="s">
+      <c r="A19" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="110"/>
-      <c r="C19" s="111"/>
+      <c r="B19" s="114"/>
+      <c r="C19" s="115"/>
       <c r="D19" s="84">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2218,11 +2218,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="128"/>
-      <c r="C21" s="87"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="103"/>
       <c r="D21" s="33"/>
       <c r="E21" s="49">
         <f>SUM(E16:E18)</f>
@@ -2265,40 +2265,40 @@
       <c r="H23" s="57"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="129" t="s">
+      <c r="A24" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="129"/>
-      <c r="C24" s="129" t="s">
+      <c r="B24" s="108"/>
+      <c r="C24" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="129"/>
-      <c r="E24" s="130" t="s">
+      <c r="D24" s="108"/>
+      <c r="E24" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="130"/>
-      <c r="G24" s="129" t="s">
+      <c r="F24" s="109"/>
+      <c r="G24" s="108" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="129"/>
+      <c r="H24" s="108"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="90" t="s">
+      <c r="B25" s="106"/>
+      <c r="C25" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="90"/>
-      <c r="E25" s="131" t="s">
+      <c r="D25" s="106"/>
+      <c r="E25" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="131"/>
-      <c r="G25" s="90" t="s">
+      <c r="F25" s="110"/>
+      <c r="G25" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="90"/>
+      <c r="H25" s="106"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
@@ -2341,25 +2341,36 @@
       <c r="H29" s="57"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="129" t="s">
+      <c r="A30" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="129"/>
-      <c r="C30" s="129" t="s">
+      <c r="B30" s="108"/>
+      <c r="C30" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="129"/>
-      <c r="E30" s="130" t="s">
+      <c r="D30" s="108"/>
+      <c r="E30" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="130"/>
-      <c r="G30" s="129" t="s">
+      <c r="F30" s="109"/>
+      <c r="G30" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="129"/>
+      <c r="H30" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A30:B30"/>
@@ -2373,17 +2384,6 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2413,55 +2413,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="140"/>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="141" t="s">
+      <c r="A1" s="144"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="147" t="s">
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="151" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="148"/>
+      <c r="H1" s="152"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="140"/>
-      <c r="B2" s="140"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="147" t="s">
+      <c r="A2" s="144"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="148"/>
+      <c r="H2" s="152"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="140"/>
-      <c r="B3" s="140"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="146"/>
-      <c r="G3" s="147" t="s">
+      <c r="A3" s="144"/>
+      <c r="B3" s="144"/>
+      <c r="C3" s="144"/>
+      <c r="D3" s="149"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="148"/>
+      <c r="H3" s="152"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="139" t="str">
+      <c r="A4" s="143" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 06 năm 2026</v>
       </c>
-      <c r="B4" s="139"/>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="139"/>
-      <c r="H4" s="139"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
@@ -2498,27 +2498,27 @@
       <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="133" t="s">
+      <c r="B8" s="153" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="135" t="s">
+      <c r="C8" s="155" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="137"/>
-      <c r="G8" s="138" t="s">
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="157"/>
+      <c r="G8" s="158" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="138"/>
+      <c r="H8" s="158"/>
       <c r="I8" s="55"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="134"/>
-      <c r="B9" s="134"/>
+      <c r="A9" s="154"/>
+      <c r="B9" s="154"/>
       <c r="C9" s="37" t="s">
         <v>61</v>
       </c>
@@ -2531,8 +2531,8 @@
       <c r="F9" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
+      <c r="G9" s="158"/>
+      <c r="H9" s="158"/>
       <c r="I9" s="55"/>
     </row>
     <row r="10" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2555,10 +2555,10 @@
         <f>D10-E10</f>
         <v>2</v>
       </c>
-      <c r="G10" s="132" t="s">
+      <c r="G10" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="132"/>
+      <c r="H10" s="136"/>
       <c r="I10" s="55"/>
     </row>
     <row r="11" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2581,10 +2581,10 @@
         <f>SUM(D11-E11)</f>
         <v>12</v>
       </c>
-      <c r="G11" s="153" t="s">
+      <c r="G11" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="154"/>
+      <c r="H11" s="133"/>
       <c r="I11" s="55"/>
     </row>
     <row r="12" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2607,10 +2607,10 @@
         <f>SUM(D12-E12)</f>
         <v>2800</v>
       </c>
-      <c r="G12" s="153" t="s">
+      <c r="G12" s="132" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="154"/>
+      <c r="H12" s="133"/>
       <c r="I12" s="55"/>
     </row>
     <row r="13" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2633,10 +2633,10 @@
         <f>D13-E13</f>
         <v>2</v>
       </c>
-      <c r="G13" s="132" t="s">
+      <c r="G13" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="132"/>
+      <c r="H13" s="136"/>
       <c r="I13" s="55"/>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2659,10 +2659,10 @@
         <f t="shared" ref="F14" si="0">D14</f>
         <v>178</v>
       </c>
-      <c r="G14" s="132" t="s">
+      <c r="G14" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="132"/>
+      <c r="H14" s="136"/>
       <c r="I14" s="55"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2685,10 +2685,10 @@
         <f>D15-E15</f>
         <v>52</v>
       </c>
-      <c r="G15" s="132" t="s">
+      <c r="G15" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="132"/>
+      <c r="H15" s="136"/>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79">
@@ -2710,10 +2710,10 @@
         <f>D16-E16</f>
         <v>22</v>
       </c>
-      <c r="G16" s="132" t="s">
+      <c r="G16" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="132"/>
+      <c r="H16" s="136"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="79">
@@ -2735,10 +2735,10 @@
         <f>D17-E17</f>
         <v>2</v>
       </c>
-      <c r="G17" s="132" t="s">
+      <c r="G17" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="132"/>
+      <c r="H17" s="136"/>
     </row>
     <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="79">
@@ -2759,10 +2759,10 @@
       <c r="F18" s="41">
         <v>3</v>
       </c>
-      <c r="G18" s="132" t="s">
+      <c r="G18" s="136" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="132"/>
+      <c r="H18" s="136"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="79">
@@ -2782,10 +2782,10 @@
         <f>SUM(D19-E19)</f>
         <v>10</v>
       </c>
-      <c r="G19" s="151" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="152"/>
+      <c r="G19" s="141" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="142"/>
     </row>
     <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="79">
@@ -2807,16 +2807,16 @@
         <f>SUM(D20-E20)</f>
         <v>59</v>
       </c>
-      <c r="G20" s="132" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="132"/>
+      <c r="G20" s="136" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="136"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="157" t="s">
+      <c r="A21" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="158"/>
+      <c r="B21" s="138"/>
       <c r="C21" s="82">
         <f>SUM(C10:C20)</f>
         <v>6460</v>
@@ -2833,8 +2833,8 @@
         <f>SUM(F10:F20)</f>
         <v>3142</v>
       </c>
-      <c r="G21" s="149"/>
-      <c r="H21" s="150"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="140"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
@@ -2847,40 +2847,40 @@
       <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="156" t="s">
+      <c r="A23" s="135" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="156"/>
-      <c r="C23" s="156" t="s">
+      <c r="B23" s="135"/>
+      <c r="C23" s="135" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156" t="s">
+      <c r="D23" s="135"/>
+      <c r="E23" s="135" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="156"/>
-      <c r="G23" s="89" t="s">
+      <c r="F23" s="135"/>
+      <c r="G23" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="89"/>
+      <c r="H23" s="105"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="90" t="s">
+      <c r="B24" s="106"/>
+      <c r="C24" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90" t="s">
+      <c r="D24" s="106"/>
+      <c r="E24" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90" t="s">
+      <c r="F24" s="106"/>
+      <c r="G24" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="90"/>
+      <c r="H24" s="106"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="32"/>
@@ -2923,22 +2923,22 @@
       <c r="H28" s="43"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="155" t="s">
+      <c r="A29" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="155"/>
-      <c r="C29" s="155" t="s">
+      <c r="B29" s="134"/>
+      <c r="C29" s="134" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="155"/>
-      <c r="E29" s="155" t="s">
+      <c r="D29" s="134"/>
+      <c r="E29" s="134" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="155"/>
-      <c r="G29" s="155" t="s">
+      <c r="F29" s="134"/>
+      <c r="G29" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="H29" s="155"/>
+      <c r="H29" s="134"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="35"/>
@@ -2952,6 +2952,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A29:B29"/>
@@ -2968,25 +2987,6 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="89" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-06-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-06-2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA81712E-AFDC-438B-B95C-7C81A1A0BCDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4D8454-03E3-46F2-A329-A0323C986D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -843,6 +843,21 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -891,19 +906,67 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -918,67 +981,63 @@
     <xf numFmtId="4" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -993,70 +1052,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1543,74 +1543,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="86"/>
-      <c r="B1" s="87"/>
-      <c r="C1" s="94" t="s">
+      <c r="A1" s="91"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="86"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="91" t="s">
+      <c r="A2" s="91"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="93"/>
+      <c r="D2" s="97"/>
+      <c r="E2" s="97"/>
+      <c r="F2" s="98"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="86"/>
-      <c r="B3" s="87"/>
-      <c r="C3" s="99" t="s">
+      <c r="A3" s="91"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="101"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="106"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="87"/>
-      <c r="C4" s="88" t="s">
+      <c r="A4" s="91"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="90"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="95"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="65"/>
       <c r="B6" s="65"/>
       <c r="C6" s="65"/>
       <c r="D6" s="66"/>
-      <c r="E6" s="96" t="str">
+      <c r="E6" s="101" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 06 năm 2026</v>
       </c>
-      <c r="F6" s="96"/>
+      <c r="F6" s="101"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="95" t="s">
+      <c r="A7" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
       <c r="F7" s="28"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1694,10 +1694,10 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="102" t="s">
+      <c r="A13" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="103"/>
+      <c r="B13" s="87"/>
       <c r="C13" s="50">
         <f>SUM(C12:C12)</f>
         <v>200</v>
@@ -1707,12 +1707,12 @@
       <c r="F13" s="46"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="104" t="s">
+      <c r="A14" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="49">
         <f>SUM(E11:E12)</f>
         <v>1746000</v>
@@ -1736,33 +1736,33 @@
       <c r="F16" s="28"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="105" t="s">
+      <c r="A17" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="105"/>
+      <c r="B17" s="89"/>
       <c r="C17" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="105" t="s">
+      <c r="D17" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="105"/>
+      <c r="E17" s="89"/>
       <c r="F17" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="106" t="s">
+      <c r="A18" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="106"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="106" t="s">
+      <c r="D18" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="106"/>
+      <c r="E18" s="90"/>
       <c r="F18" s="27" t="s">
         <v>7</v>
       </c>
@@ -1800,17 +1800,17 @@
       <c r="F22" s="22"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="105" t="s">
+      <c r="A23" s="89" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="105"/>
+      <c r="B23" s="89"/>
       <c r="C23" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D23" s="105" t="s">
+      <c r="D23" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="105"/>
+      <c r="E23" s="89"/>
       <c r="F23" s="9" t="s">
         <v>9</v>
       </c>
@@ -1849,6 +1849,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A17:B17"/>
@@ -1857,14 +1865,6 @@
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C3:F3"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1897,64 +1897,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="118"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="120" t="s">
+      <c r="A1" s="114"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="116"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="118"/>
-      <c r="B2" s="119"/>
-      <c r="C2" s="129" t="s">
+      <c r="A2" s="114"/>
+      <c r="B2" s="115"/>
+      <c r="C2" s="125" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="131"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="127"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="118"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="99" t="s">
+      <c r="A3" s="114"/>
+      <c r="B3" s="115"/>
+      <c r="C3" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="100"/>
-      <c r="E3" s="100"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="101"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="105"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="106"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="118"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="88" t="s">
+      <c r="A4" s="114"/>
+      <c r="B4" s="115"/>
+      <c r="C4" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="90"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="95"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="121" t="s">
+      <c r="A5" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="122"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="123"/>
-      <c r="F5" s="123"/>
-      <c r="G5" s="123"/>
-      <c r="H5" s="124"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="120"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="70"/>
@@ -2003,10 +2003,10 @@
       <c r="H9" s="28"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="125" t="s">
+      <c r="A10" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="126"/>
+      <c r="B10" s="122"/>
       <c r="C10" s="48">
         <f>'Bảng tính CK'!E14</f>
         <v>1746000</v>
@@ -2018,10 +2018,10 @@
       <c r="H10" s="28"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="111" t="s">
+      <c r="A11" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="112"/>
+      <c r="B11" s="108"/>
       <c r="C11" s="48">
         <v>3</v>
       </c>
@@ -2032,10 +2032,10 @@
       <c r="H11" s="28"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="127" t="s">
+      <c r="A12" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="128"/>
+      <c r="B12" s="124"/>
       <c r="C12" s="46">
         <v>1</v>
       </c>
@@ -2046,10 +2046,10 @@
       <c r="H12" s="28"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="116" t="s">
+      <c r="A13" s="112" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="117"/>
+      <c r="B13" s="113"/>
       <c r="C13" s="46">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>0</v>
@@ -2181,11 +2181,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="114"/>
-      <c r="C19" s="115"/>
+      <c r="B19" s="110"/>
+      <c r="C19" s="111"/>
       <c r="D19" s="84">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2218,11 +2218,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="102" t="s">
+      <c r="A21" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="107"/>
-      <c r="C21" s="103"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="33"/>
       <c r="E21" s="49">
         <f>SUM(E16:E18)</f>
@@ -2265,40 +2265,40 @@
       <c r="H23" s="57"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="108" t="s">
+      <c r="A24" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="108"/>
-      <c r="C24" s="108" t="s">
+      <c r="B24" s="129"/>
+      <c r="C24" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="108"/>
-      <c r="E24" s="109" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="109"/>
-      <c r="G24" s="108" t="s">
+      <c r="F24" s="130"/>
+      <c r="G24" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="108"/>
+      <c r="H24" s="129"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="106" t="s">
+      <c r="A25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="106"/>
-      <c r="C25" s="106" t="s">
+      <c r="B25" s="90"/>
+      <c r="C25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="106"/>
-      <c r="E25" s="110" t="s">
+      <c r="D25" s="90"/>
+      <c r="E25" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="110"/>
-      <c r="G25" s="106" t="s">
+      <c r="F25" s="131"/>
+      <c r="G25" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="106"/>
+      <c r="H25" s="90"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="56"/>
@@ -2341,36 +2341,25 @@
       <c r="H29" s="57"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="108" t="s">
+      <c r="A30" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="108"/>
-      <c r="C30" s="108" t="s">
+      <c r="B30" s="129"/>
+      <c r="C30" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="108"/>
-      <c r="E30" s="109" t="s">
+      <c r="D30" s="129"/>
+      <c r="E30" s="130" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="109"/>
-      <c r="G30" s="108" t="s">
+      <c r="F30" s="130"/>
+      <c r="G30" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="108"/>
+      <c r="H30" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A30:B30"/>
@@ -2384,6 +2373,17 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2413,55 +2413,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="144"/>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="145" t="s">
+      <c r="A1" s="140"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="151" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="152"/>
+      <c r="H1" s="148"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="144"/>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
-      <c r="G2" s="151" t="s">
+      <c r="A2" s="140"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="147" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="152"/>
+      <c r="H2" s="148"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="144"/>
-      <c r="B3" s="144"/>
-      <c r="C3" s="144"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="151" t="s">
+      <c r="A3" s="140"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="152"/>
+      <c r="H3" s="148"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="143" t="str">
+      <c r="A4" s="139" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 06 năm 2026</v>
       </c>
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
@@ -2498,27 +2498,27 @@
       <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="153" t="s">
+      <c r="A8" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="153" t="s">
+      <c r="B8" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="155" t="s">
+      <c r="C8" s="135" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="156"/>
-      <c r="E8" s="156"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="158" t="s">
+      <c r="D8" s="136"/>
+      <c r="E8" s="136"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="138" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="158"/>
+      <c r="H8" s="138"/>
       <c r="I8" s="55"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="154"/>
-      <c r="B9" s="154"/>
+      <c r="A9" s="134"/>
+      <c r="B9" s="134"/>
       <c r="C9" s="37" t="s">
         <v>61</v>
       </c>
@@ -2531,8 +2531,8 @@
       <c r="F9" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="158"/>
-      <c r="H9" s="158"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
       <c r="I9" s="55"/>
     </row>
     <row r="10" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2555,10 +2555,10 @@
         <f>D10-E10</f>
         <v>2</v>
       </c>
-      <c r="G10" s="136" t="s">
+      <c r="G10" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="136"/>
+      <c r="H10" s="132"/>
       <c r="I10" s="55"/>
     </row>
     <row r="11" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2581,10 +2581,10 @@
         <f>SUM(D11-E11)</f>
         <v>12</v>
       </c>
-      <c r="G11" s="132" t="s">
+      <c r="G11" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="133"/>
+      <c r="H11" s="154"/>
       <c r="I11" s="55"/>
     </row>
     <row r="12" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2607,10 +2607,10 @@
         <f>SUM(D12-E12)</f>
         <v>2800</v>
       </c>
-      <c r="G12" s="132" t="s">
+      <c r="G12" s="153" t="s">
         <v>66</v>
       </c>
-      <c r="H12" s="133"/>
+      <c r="H12" s="154"/>
       <c r="I12" s="55"/>
     </row>
     <row r="13" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2633,10 +2633,10 @@
         <f>D13-E13</f>
         <v>2</v>
       </c>
-      <c r="G13" s="136" t="s">
+      <c r="G13" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="136"/>
+      <c r="H13" s="132"/>
       <c r="I13" s="55"/>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2659,10 +2659,10 @@
         <f t="shared" ref="F14" si="0">D14</f>
         <v>178</v>
       </c>
-      <c r="G14" s="136" t="s">
+      <c r="G14" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="136"/>
+      <c r="H14" s="132"/>
       <c r="I14" s="55"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2685,10 +2685,10 @@
         <f>D15-E15</f>
         <v>52</v>
       </c>
-      <c r="G15" s="136" t="s">
+      <c r="G15" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="136"/>
+      <c r="H15" s="132"/>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79">
@@ -2710,10 +2710,10 @@
         <f>D16-E16</f>
         <v>22</v>
       </c>
-      <c r="G16" s="136" t="s">
+      <c r="G16" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="136"/>
+      <c r="H16" s="132"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="79">
@@ -2735,10 +2735,10 @@
         <f>D17-E17</f>
         <v>2</v>
       </c>
-      <c r="G17" s="136" t="s">
+      <c r="G17" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="136"/>
+      <c r="H17" s="132"/>
     </row>
     <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="79">
@@ -2759,10 +2759,10 @@
       <c r="F18" s="41">
         <v>3</v>
       </c>
-      <c r="G18" s="136" t="s">
+      <c r="G18" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="136"/>
+      <c r="H18" s="132"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="79">
@@ -2782,10 +2782,10 @@
         <f>SUM(D19-E19)</f>
         <v>10</v>
       </c>
-      <c r="G19" s="141" t="s">
+      <c r="G19" s="151" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="142"/>
+      <c r="H19" s="152"/>
     </row>
     <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="79">
@@ -2807,16 +2807,16 @@
         <f>SUM(D20-E20)</f>
         <v>59</v>
       </c>
-      <c r="G20" s="136" t="s">
+      <c r="G20" s="132" t="s">
         <v>76</v>
       </c>
-      <c r="H20" s="136"/>
+      <c r="H20" s="132"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="137" t="s">
+      <c r="A21" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="138"/>
+      <c r="B21" s="158"/>
       <c r="C21" s="82">
         <f>SUM(C10:C20)</f>
         <v>6460</v>
@@ -2833,8 +2833,8 @@
         <f>SUM(F10:F20)</f>
         <v>3142</v>
       </c>
-      <c r="G21" s="139"/>
-      <c r="H21" s="140"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="150"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="18"/>
@@ -2847,40 +2847,40 @@
       <c r="H22" s="18"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="135" t="s">
+      <c r="A23" s="156" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="135"/>
-      <c r="C23" s="135" t="s">
+      <c r="B23" s="156"/>
+      <c r="C23" s="156" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="135"/>
-      <c r="E23" s="135" t="s">
+      <c r="D23" s="156"/>
+      <c r="E23" s="156" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="135"/>
-      <c r="G23" s="105" t="s">
+      <c r="F23" s="156"/>
+      <c r="G23" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="105"/>
+      <c r="H23" s="89"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="106" t="s">
+      <c r="A24" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="106" t="s">
+      <c r="B24" s="90"/>
+      <c r="C24" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="106"/>
-      <c r="E24" s="106" t="s">
+      <c r="D24" s="90"/>
+      <c r="E24" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="106"/>
-      <c r="G24" s="106" t="s">
+      <c r="F24" s="90"/>
+      <c r="G24" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="106"/>
+      <c r="H24" s="90"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="32"/>
@@ -2923,22 +2923,22 @@
       <c r="H28" s="43"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="134" t="s">
+      <c r="A29" s="155" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="134"/>
-      <c r="C29" s="134" t="s">
+      <c r="B29" s="155"/>
+      <c r="C29" s="155" t="s">
         <v>34</v>
       </c>
-      <c r="D29" s="134"/>
-      <c r="E29" s="134" t="s">
+      <c r="D29" s="155"/>
+      <c r="E29" s="155" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="134"/>
-      <c r="G29" s="134" t="s">
+      <c r="F29" s="155"/>
+      <c r="G29" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="H29" s="134"/>
+      <c r="H29" s="155"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="35"/>
@@ -2952,25 +2952,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A29:B29"/>
@@ -2987,6 +2968,25 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="A21:B21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="89" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
